--- a/Techniques/Model based and Residual Monitoring/outputs/G11/dsas_g11_bearings_vibration_temp_deviation_monitoring/deviation_monitoring/dsas_g11_bearings_vibration_temp_deviation_monitoring_output3.xlsx
+++ b/Techniques/Model based and Residual Monitoring/outputs/G11/dsas_g11_bearings_vibration_temp_deviation_monitoring/deviation_monitoring/dsas_g11_bearings_vibration_temp_deviation_monitoring_output3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -417,93 +429,98 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q120"/>
+  <dimension ref="A1:R120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9343</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9344</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9357</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9358</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9359</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9360</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9361</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9368</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9369</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9370</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9408</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>RecordDate</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>RecordTime</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>System_Deviation_Index</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Is_Anomaly</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Anomaly_Label</t>
         </is>
       </c>
     </row>
@@ -544,10 +561,10 @@
       <c r="L2" t="n">
         <v>6.3</v>
       </c>
-      <c r="M2" s="1" t="n">
+      <c r="M2" s="2" t="n">
         <v>46126.35861111111</v>
       </c>
-      <c r="N2" s="1" t="n">
+      <c r="N2" s="2" t="n">
         <v>46126</v>
       </c>
       <c r="O2" t="inlineStr">
@@ -560,6 +577,11 @@
       </c>
       <c r="Q2" t="b">
         <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -599,10 +621,10 @@
       <c r="L3" t="n">
         <v>6.5</v>
       </c>
-      <c r="M3" s="1" t="n">
+      <c r="M3" s="2" t="n">
         <v>46126.53461805556</v>
       </c>
-      <c r="N3" s="1" t="n">
+      <c r="N3" s="2" t="n">
         <v>46126</v>
       </c>
       <c r="O3" t="inlineStr">
@@ -615,6 +637,11 @@
       </c>
       <c r="Q3" t="b">
         <v>0</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -654,10 +681,10 @@
       <c r="L4" t="n">
         <v>6.5</v>
       </c>
-      <c r="M4" s="1" t="n">
+      <c r="M4" s="2" t="n">
         <v>46126.70118055555</v>
       </c>
-      <c r="N4" s="1" t="n">
+      <c r="N4" s="2" t="n">
         <v>46126</v>
       </c>
       <c r="O4" t="inlineStr">
@@ -670,6 +697,11 @@
       </c>
       <c r="Q4" t="b">
         <v>0</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -709,10 +741,10 @@
       <c r="L5" t="n">
         <v>6.5</v>
       </c>
-      <c r="M5" s="1" t="n">
+      <c r="M5" s="2" t="n">
         <v>46126.87692129629</v>
       </c>
-      <c r="N5" s="1" t="n">
+      <c r="N5" s="2" t="n">
         <v>46126</v>
       </c>
       <c r="O5" t="inlineStr">
@@ -725,6 +757,11 @@
       </c>
       <c r="Q5" t="b">
         <v>0</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -764,10 +801,10 @@
       <c r="L6" t="n">
         <v>6.4</v>
       </c>
-      <c r="M6" s="1" t="n">
+      <c r="M6" s="2" t="n">
         <v>46127.02172453704</v>
       </c>
-      <c r="N6" s="1" t="n">
+      <c r="N6" s="2" t="n">
         <v>46127</v>
       </c>
       <c r="O6" t="inlineStr">
@@ -780,6 +817,11 @@
       </c>
       <c r="Q6" t="b">
         <v>0</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -819,10 +861,10 @@
       <c r="L7" t="n">
         <v>2.5</v>
       </c>
-      <c r="M7" s="1" t="n">
+      <c r="M7" s="2" t="n">
         <v>46127.20758101852</v>
       </c>
-      <c r="N7" s="1" t="n">
+      <c r="N7" s="2" t="n">
         <v>46127</v>
       </c>
       <c r="O7" t="inlineStr">
@@ -835,6 +877,11 @@
       </c>
       <c r="Q7" t="b">
         <v>0</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -874,10 +921,10 @@
       <c r="L8" t="n">
         <v>2.4</v>
       </c>
-      <c r="M8" s="1" t="n">
+      <c r="M8" s="2" t="n">
         <v>46127.35572916667</v>
       </c>
-      <c r="N8" s="1" t="n">
+      <c r="N8" s="2" t="n">
         <v>46127</v>
       </c>
       <c r="O8" t="inlineStr">
@@ -890,6 +937,11 @@
       </c>
       <c r="Q8" t="b">
         <v>0</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -929,10 +981,10 @@
       <c r="L9" t="n">
         <v>2.4</v>
       </c>
-      <c r="M9" s="1" t="n">
+      <c r="M9" s="2" t="n">
         <v>46127.53050925926</v>
       </c>
-      <c r="N9" s="1" t="n">
+      <c r="N9" s="2" t="n">
         <v>46127</v>
       </c>
       <c r="O9" t="inlineStr">
@@ -945,6 +997,11 @@
       </c>
       <c r="Q9" t="b">
         <v>0</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -984,10 +1041,10 @@
       <c r="L10" t="n">
         <v>6.6</v>
       </c>
-      <c r="M10" s="1" t="n">
+      <c r="M10" s="2" t="n">
         <v>46127.69168981481</v>
       </c>
-      <c r="N10" s="1" t="n">
+      <c r="N10" s="2" t="n">
         <v>46127</v>
       </c>
       <c r="O10" t="inlineStr">
@@ -1000,6 +1057,11 @@
       </c>
       <c r="Q10" t="b">
         <v>0</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1039,10 +1101,10 @@
       <c r="L11" t="n">
         <v>6.7</v>
       </c>
-      <c r="M11" s="1" t="n">
+      <c r="M11" s="2" t="n">
         <v>46127.85546296297</v>
       </c>
-      <c r="N11" s="1" t="n">
+      <c r="N11" s="2" t="n">
         <v>46127</v>
       </c>
       <c r="O11" t="inlineStr">
@@ -1055,6 +1117,11 @@
       </c>
       <c r="Q11" t="b">
         <v>0</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1094,10 +1161,10 @@
       <c r="L12" t="n">
         <v>6.6</v>
       </c>
-      <c r="M12" s="1" t="n">
+      <c r="M12" s="2" t="n">
         <v>46128.04122685185</v>
       </c>
-      <c r="N12" s="1" t="n">
+      <c r="N12" s="2" t="n">
         <v>46128</v>
       </c>
       <c r="O12" t="inlineStr">
@@ -1110,6 +1177,11 @@
       </c>
       <c r="Q12" t="b">
         <v>0</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1149,10 +1221,10 @@
       <c r="L13" t="n">
         <v>6.6</v>
       </c>
-      <c r="M13" s="1" t="n">
+      <c r="M13" s="2" t="n">
         <v>46128.19846064815</v>
       </c>
-      <c r="N13" s="1" t="n">
+      <c r="N13" s="2" t="n">
         <v>46128</v>
       </c>
       <c r="O13" t="inlineStr">
@@ -1165,6 +1237,11 @@
       </c>
       <c r="Q13" t="b">
         <v>0</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1204,10 +1281,10 @@
       <c r="L14" t="n">
         <v>6.6</v>
       </c>
-      <c r="M14" s="1" t="n">
+      <c r="M14" s="2" t="n">
         <v>46128.3578125</v>
       </c>
-      <c r="N14" s="1" t="n">
+      <c r="N14" s="2" t="n">
         <v>46128</v>
       </c>
       <c r="O14" t="inlineStr">
@@ -1220,6 +1297,11 @@
       </c>
       <c r="Q14" t="b">
         <v>0</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1259,10 +1341,10 @@
       <c r="L15" t="n">
         <v>6.7</v>
       </c>
-      <c r="M15" s="1" t="n">
+      <c r="M15" s="2" t="n">
         <v>46128.52149305555</v>
       </c>
-      <c r="N15" s="1" t="n">
+      <c r="N15" s="2" t="n">
         <v>46128</v>
       </c>
       <c r="O15" t="inlineStr">
@@ -1275,6 +1357,11 @@
       </c>
       <c r="Q15" t="b">
         <v>0</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1314,10 +1401,10 @@
       <c r="L16" t="n">
         <v>2.4</v>
       </c>
-      <c r="M16" s="1" t="n">
+      <c r="M16" s="2" t="n">
         <v>46128.69186342593</v>
       </c>
-      <c r="N16" s="1" t="n">
+      <c r="N16" s="2" t="n">
         <v>46128</v>
       </c>
       <c r="O16" t="inlineStr">
@@ -1330,6 +1417,11 @@
       </c>
       <c r="Q16" t="b">
         <v>0</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1369,10 +1461,10 @@
       <c r="L17" t="n">
         <v>2.4</v>
       </c>
-      <c r="M17" s="1" t="n">
+      <c r="M17" s="2" t="n">
         <v>46128.85454861111</v>
       </c>
-      <c r="N17" s="1" t="n">
+      <c r="N17" s="2" t="n">
         <v>46128</v>
       </c>
       <c r="O17" t="inlineStr">
@@ -1385,6 +1477,11 @@
       </c>
       <c r="Q17" t="b">
         <v>0</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1424,10 +1521,10 @@
       <c r="L18" t="n">
         <v>2.4</v>
       </c>
-      <c r="M18" s="1" t="n">
+      <c r="M18" s="2" t="n">
         <v>46129.08709490741</v>
       </c>
-      <c r="N18" s="1" t="n">
+      <c r="N18" s="2" t="n">
         <v>46129</v>
       </c>
       <c r="O18" t="inlineStr">
@@ -1440,6 +1537,11 @@
       </c>
       <c r="Q18" t="b">
         <v>0</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1479,10 +1581,10 @@
       <c r="L19" t="n">
         <v>6.8</v>
       </c>
-      <c r="M19" s="1" t="n">
+      <c r="M19" s="2" t="n">
         <v>46129.20550925926</v>
       </c>
-      <c r="N19" s="1" t="n">
+      <c r="N19" s="2" t="n">
         <v>46129</v>
       </c>
       <c r="O19" t="inlineStr">
@@ -1495,6 +1597,11 @@
       </c>
       <c r="Q19" t="b">
         <v>0</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1534,10 +1641,10 @@
       <c r="L20" t="n">
         <v>6.7</v>
       </c>
-      <c r="M20" s="1" t="n">
+      <c r="M20" s="2" t="n">
         <v>46129.36481481481</v>
       </c>
-      <c r="N20" s="1" t="n">
+      <c r="N20" s="2" t="n">
         <v>46129</v>
       </c>
       <c r="O20" t="inlineStr">
@@ -1550,6 +1657,11 @@
       </c>
       <c r="Q20" t="b">
         <v>0</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1589,10 +1701,10 @@
       <c r="L21" t="n">
         <v>6.7</v>
       </c>
-      <c r="M21" s="1" t="n">
+      <c r="M21" s="2" t="n">
         <v>46129.52703703703</v>
       </c>
-      <c r="N21" s="1" t="n">
+      <c r="N21" s="2" t="n">
         <v>46129</v>
       </c>
       <c r="O21" t="inlineStr">
@@ -1605,6 +1717,11 @@
       </c>
       <c r="Q21" t="b">
         <v>0</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1644,10 +1761,10 @@
       <c r="L22" t="n">
         <v>6.7</v>
       </c>
-      <c r="M22" s="1" t="n">
+      <c r="M22" s="2" t="n">
         <v>46129.69325231481</v>
       </c>
-      <c r="N22" s="1" t="n">
+      <c r="N22" s="2" t="n">
         <v>46129</v>
       </c>
       <c r="O22" t="inlineStr">
@@ -1660,6 +1777,11 @@
       </c>
       <c r="Q22" t="b">
         <v>0</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1699,10 +1821,10 @@
       <c r="L23" t="n">
         <v>6.7</v>
       </c>
-      <c r="M23" s="1" t="n">
+      <c r="M23" s="2" t="n">
         <v>46129.85914351852</v>
       </c>
-      <c r="N23" s="1" t="n">
+      <c r="N23" s="2" t="n">
         <v>46129</v>
       </c>
       <c r="O23" t="inlineStr">
@@ -1715,6 +1837,11 @@
       </c>
       <c r="Q23" t="b">
         <v>0</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1754,10 +1881,10 @@
       <c r="L24" t="n">
         <v>6.7</v>
       </c>
-      <c r="M24" s="1" t="n">
+      <c r="M24" s="2" t="n">
         <v>46130.09744212963</v>
       </c>
-      <c r="N24" s="1" t="n">
+      <c r="N24" s="2" t="n">
         <v>46130</v>
       </c>
       <c r="O24" t="inlineStr">
@@ -1770,6 +1897,11 @@
       </c>
       <c r="Q24" t="b">
         <v>0</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1809,10 +1941,10 @@
       <c r="L25" t="n">
         <v>6.7</v>
       </c>
-      <c r="M25" s="1" t="n">
+      <c r="M25" s="2" t="n">
         <v>46130.19385416667</v>
       </c>
-      <c r="N25" s="1" t="n">
+      <c r="N25" s="2" t="n">
         <v>46130</v>
       </c>
       <c r="O25" t="inlineStr">
@@ -1825,6 +1957,11 @@
       </c>
       <c r="Q25" t="b">
         <v>0</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1864,10 +2001,10 @@
       <c r="L26" t="n">
         <v>6.7</v>
       </c>
-      <c r="M26" s="1" t="n">
+      <c r="M26" s="2" t="n">
         <v>46130.35618055556</v>
       </c>
-      <c r="N26" s="1" t="n">
+      <c r="N26" s="2" t="n">
         <v>46130</v>
       </c>
       <c r="O26" t="inlineStr">
@@ -1880,6 +2017,11 @@
       </c>
       <c r="Q26" t="b">
         <v>0</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -1919,10 +2061,10 @@
       <c r="L27" t="n">
         <v>6.7</v>
       </c>
-      <c r="M27" s="1" t="n">
+      <c r="M27" s="2" t="n">
         <v>46130.52403935185</v>
       </c>
-      <c r="N27" s="1" t="n">
+      <c r="N27" s="2" t="n">
         <v>46130</v>
       </c>
       <c r="O27" t="inlineStr">
@@ -1935,6 +2077,11 @@
       </c>
       <c r="Q27" t="b">
         <v>0</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -1974,10 +2121,10 @@
       <c r="L28" t="n">
         <v>7</v>
       </c>
-      <c r="M28" s="1" t="n">
+      <c r="M28" s="2" t="n">
         <v>46130.68988425926</v>
       </c>
-      <c r="N28" s="1" t="n">
+      <c r="N28" s="2" t="n">
         <v>46130</v>
       </c>
       <c r="O28" t="inlineStr">
@@ -1990,6 +2137,11 @@
       </c>
       <c r="Q28" t="b">
         <v>1</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>⚠️ Anomaly</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -2029,10 +2181,10 @@
       <c r="L29" t="n">
         <v>7</v>
       </c>
-      <c r="M29" s="1" t="n">
+      <c r="M29" s="2" t="n">
         <v>46131.02777777778</v>
       </c>
-      <c r="N29" s="1" t="n">
+      <c r="N29" s="2" t="n">
         <v>46131</v>
       </c>
       <c r="O29" t="inlineStr">
@@ -2045,6 +2197,11 @@
       </c>
       <c r="Q29" t="b">
         <v>0</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -2084,10 +2241,10 @@
       <c r="L30" t="n">
         <v>2.4</v>
       </c>
-      <c r="M30" s="1" t="n">
+      <c r="M30" s="2" t="n">
         <v>46131.19017361111</v>
       </c>
-      <c r="N30" s="1" t="n">
+      <c r="N30" s="2" t="n">
         <v>46131</v>
       </c>
       <c r="O30" t="inlineStr">
@@ -2100,6 +2257,11 @@
       </c>
       <c r="Q30" t="b">
         <v>1</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>⚠️ Anomaly</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -2139,10 +2301,10 @@
       <c r="L31" t="n">
         <v>2.4</v>
       </c>
-      <c r="M31" s="1" t="n">
+      <c r="M31" s="2" t="n">
         <v>46131.35472222222</v>
       </c>
-      <c r="N31" s="1" t="n">
+      <c r="N31" s="2" t="n">
         <v>46131</v>
       </c>
       <c r="O31" t="inlineStr">
@@ -2155,6 +2317,11 @@
       </c>
       <c r="Q31" t="b">
         <v>0</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -2194,10 +2361,10 @@
       <c r="L32" t="n">
         <v>2.4</v>
       </c>
-      <c r="M32" s="1" t="n">
+      <c r="M32" s="2" t="n">
         <v>46131.52929398148</v>
       </c>
-      <c r="N32" s="1" t="n">
+      <c r="N32" s="2" t="n">
         <v>46131</v>
       </c>
       <c r="O32" t="inlineStr">
@@ -2210,6 +2377,11 @@
       </c>
       <c r="Q32" t="b">
         <v>0</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -2249,10 +2421,10 @@
       <c r="L33" t="n">
         <v>6.8</v>
       </c>
-      <c r="M33" s="1" t="n">
+      <c r="M33" s="2" t="n">
         <v>46131.68760416667</v>
       </c>
-      <c r="N33" s="1" t="n">
+      <c r="N33" s="2" t="n">
         <v>46131</v>
       </c>
       <c r="O33" t="inlineStr">
@@ -2265,6 +2437,11 @@
       </c>
       <c r="Q33" t="b">
         <v>0</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -2304,10 +2481,10 @@
       <c r="L34" t="n">
         <v>6.8</v>
       </c>
-      <c r="M34" s="1" t="n">
+      <c r="M34" s="2" t="n">
         <v>46131.8633912037</v>
       </c>
-      <c r="N34" s="1" t="n">
+      <c r="N34" s="2" t="n">
         <v>46131</v>
       </c>
       <c r="O34" t="inlineStr">
@@ -2320,6 +2497,11 @@
       </c>
       <c r="Q34" t="b">
         <v>1</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>⚠️ Anomaly</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -2359,10 +2541,10 @@
       <c r="L35" t="n">
         <v>6.8</v>
       </c>
-      <c r="M35" s="1" t="n">
+      <c r="M35" s="2" t="n">
         <v>46132.02103009259</v>
       </c>
-      <c r="N35" s="1" t="n">
+      <c r="N35" s="2" t="n">
         <v>46132</v>
       </c>
       <c r="O35" t="inlineStr">
@@ -2375,6 +2557,11 @@
       </c>
       <c r="Q35" t="b">
         <v>0</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -2414,10 +2601,10 @@
       <c r="L36" t="n">
         <v>7</v>
       </c>
-      <c r="M36" s="1" t="n">
+      <c r="M36" s="2" t="n">
         <v>46132.19717592592</v>
       </c>
-      <c r="N36" s="1" t="n">
+      <c r="N36" s="2" t="n">
         <v>46132</v>
       </c>
       <c r="O36" t="inlineStr">
@@ -2430,6 +2617,11 @@
       </c>
       <c r="Q36" t="b">
         <v>0</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -2469,10 +2661,10 @@
       <c r="L37" t="n">
         <v>6.9</v>
       </c>
-      <c r="M37" s="1" t="n">
+      <c r="M37" s="2" t="n">
         <v>46132.3584375</v>
       </c>
-      <c r="N37" s="1" t="n">
+      <c r="N37" s="2" t="n">
         <v>46132</v>
       </c>
       <c r="O37" t="inlineStr">
@@ -2485,6 +2677,11 @@
       </c>
       <c r="Q37" t="b">
         <v>0</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -2524,10 +2721,10 @@
       <c r="L38" t="n">
         <v>6.9</v>
       </c>
-      <c r="M38" s="1" t="n">
+      <c r="M38" s="2" t="n">
         <v>46132.52159722222</v>
       </c>
-      <c r="N38" s="1" t="n">
+      <c r="N38" s="2" t="n">
         <v>46132</v>
       </c>
       <c r="O38" t="inlineStr">
@@ -2540,6 +2737,11 @@
       </c>
       <c r="Q38" t="b">
         <v>0</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -2579,10 +2781,10 @@
       <c r="L39" t="n">
         <v>2.8</v>
       </c>
-      <c r="M39" s="1" t="n">
+      <c r="M39" s="2" t="n">
         <v>46132.69394675926</v>
       </c>
-      <c r="N39" s="1" t="n">
+      <c r="N39" s="2" t="n">
         <v>46132</v>
       </c>
       <c r="O39" t="inlineStr">
@@ -2595,6 +2797,11 @@
       </c>
       <c r="Q39" t="b">
         <v>0</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -2634,10 +2841,10 @@
       <c r="L40" t="n">
         <v>2.5</v>
       </c>
-      <c r="M40" s="1" t="n">
+      <c r="M40" s="2" t="n">
         <v>46132.86247685185</v>
       </c>
-      <c r="N40" s="1" t="n">
+      <c r="N40" s="2" t="n">
         <v>46132</v>
       </c>
       <c r="O40" t="inlineStr">
@@ -2650,6 +2857,11 @@
       </c>
       <c r="Q40" t="b">
         <v>0</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -2689,10 +2901,10 @@
       <c r="L41" t="n">
         <v>2.5</v>
       </c>
-      <c r="M41" s="1" t="n">
+      <c r="M41" s="2" t="n">
         <v>46133.07111111111</v>
       </c>
-      <c r="N41" s="1" t="n">
+      <c r="N41" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="O41" t="inlineStr">
@@ -2705,6 +2917,11 @@
       </c>
       <c r="Q41" t="b">
         <v>0</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -2744,10 +2961,10 @@
       <c r="L42" t="n">
         <v>7</v>
       </c>
-      <c r="M42" s="1" t="n">
+      <c r="M42" s="2" t="n">
         <v>46133.19524305555</v>
       </c>
-      <c r="N42" s="1" t="n">
+      <c r="N42" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="O42" t="inlineStr">
@@ -2760,6 +2977,11 @@
       </c>
       <c r="Q42" t="b">
         <v>0</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -2799,10 +3021,10 @@
       <c r="L43" t="n">
         <v>7</v>
       </c>
-      <c r="M43" s="1" t="n">
+      <c r="M43" s="2" t="n">
         <v>46133.36118055556</v>
       </c>
-      <c r="N43" s="1" t="n">
+      <c r="N43" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="O43" t="inlineStr">
@@ -2815,6 +3037,11 @@
       </c>
       <c r="Q43" t="b">
         <v>0</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -2854,10 +3081,10 @@
       <c r="L44" t="n">
         <v>7</v>
       </c>
-      <c r="M44" s="1" t="n">
+      <c r="M44" s="2" t="n">
         <v>46133.52528935186</v>
       </c>
-      <c r="N44" s="1" t="n">
+      <c r="N44" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="O44" t="inlineStr">
@@ -2870,6 +3097,11 @@
       </c>
       <c r="Q44" t="b">
         <v>0</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -2909,10 +3141,10 @@
       <c r="L45" t="n">
         <v>7</v>
       </c>
-      <c r="M45" s="1" t="n">
+      <c r="M45" s="2" t="n">
         <v>46133.69530092592</v>
       </c>
-      <c r="N45" s="1" t="n">
+      <c r="N45" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="O45" t="inlineStr">
@@ -2925,6 +3157,11 @@
       </c>
       <c r="Q45" t="b">
         <v>0</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -2964,10 +3201,10 @@
       <c r="L46" t="n">
         <v>7</v>
       </c>
-      <c r="M46" s="1" t="n">
+      <c r="M46" s="2" t="n">
         <v>46133.85505787037</v>
       </c>
-      <c r="N46" s="1" t="n">
+      <c r="N46" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="O46" t="inlineStr">
@@ -2980,6 +3217,11 @@
       </c>
       <c r="Q46" t="b">
         <v>0</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -3019,10 +3261,10 @@
       <c r="L47" t="n">
         <v>7</v>
       </c>
-      <c r="M47" s="1" t="n">
+      <c r="M47" s="2" t="n">
         <v>46134.09811342593</v>
       </c>
-      <c r="N47" s="1" t="n">
+      <c r="N47" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="O47" t="inlineStr">
@@ -3035,6 +3277,11 @@
       </c>
       <c r="Q47" t="b">
         <v>0</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -3074,10 +3321,10 @@
       <c r="L48" t="n">
         <v>6.9</v>
       </c>
-      <c r="M48" s="1" t="n">
+      <c r="M48" s="2" t="n">
         <v>46134.21712962963</v>
       </c>
-      <c r="N48" s="1" t="n">
+      <c r="N48" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="O48" t="inlineStr">
@@ -3090,6 +3337,11 @@
       </c>
       <c r="Q48" t="b">
         <v>0</v>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -3129,10 +3381,10 @@
       <c r="L49" t="n">
         <v>6.9</v>
       </c>
-      <c r="M49" s="1" t="n">
+      <c r="M49" s="2" t="n">
         <v>46134.35688657407</v>
       </c>
-      <c r="N49" s="1" t="n">
+      <c r="N49" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="O49" t="inlineStr">
@@ -3145,6 +3397,11 @@
       </c>
       <c r="Q49" t="b">
         <v>0</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -3184,10 +3441,10 @@
       <c r="L50" t="n">
         <v>6.9</v>
       </c>
-      <c r="M50" s="1" t="n">
+      <c r="M50" s="2" t="n">
         <v>46134.52453703704</v>
       </c>
-      <c r="N50" s="1" t="n">
+      <c r="N50" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="O50" t="inlineStr">
@@ -3200,6 +3457,11 @@
       </c>
       <c r="Q50" t="b">
         <v>0</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -3239,10 +3501,10 @@
       <c r="L51" t="n">
         <v>7</v>
       </c>
-      <c r="M51" s="1" t="n">
+      <c r="M51" s="2" t="n">
         <v>46134.72311342593</v>
       </c>
-      <c r="N51" s="1" t="n">
+      <c r="N51" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="O51" t="inlineStr">
@@ -3255,6 +3517,11 @@
       </c>
       <c r="Q51" t="b">
         <v>0</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -3294,10 +3561,10 @@
       <c r="L52" t="n">
         <v>7.2</v>
       </c>
-      <c r="M52" s="1" t="n">
+      <c r="M52" s="2" t="n">
         <v>46134.85905092592</v>
       </c>
-      <c r="N52" s="1" t="n">
+      <c r="N52" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="O52" t="inlineStr">
@@ -3310,6 +3577,11 @@
       </c>
       <c r="Q52" t="b">
         <v>0</v>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -3349,10 +3621,10 @@
       <c r="L53" t="n">
         <v>7.2</v>
       </c>
-      <c r="M53" s="1" t="n">
+      <c r="M53" s="2" t="n">
         <v>46135.02693287037</v>
       </c>
-      <c r="N53" s="1" t="n">
+      <c r="N53" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="O53" t="inlineStr">
@@ -3365,6 +3637,11 @@
       </c>
       <c r="Q53" t="b">
         <v>1</v>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>⚠️ Anomaly</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -3404,10 +3681,10 @@
       <c r="L54" t="n">
         <v>2.7</v>
       </c>
-      <c r="M54" s="1" t="n">
+      <c r="M54" s="2" t="n">
         <v>46135.19215277778</v>
       </c>
-      <c r="N54" s="1" t="n">
+      <c r="N54" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="O54" t="inlineStr">
@@ -3420,6 +3697,11 @@
       </c>
       <c r="Q54" t="b">
         <v>1</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>⚠️ Anomaly</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -3459,10 +3741,10 @@
       <c r="L55" t="n">
         <v>2.4</v>
       </c>
-      <c r="M55" s="1" t="n">
+      <c r="M55" s="2" t="n">
         <v>46135.3603125</v>
       </c>
-      <c r="N55" s="1" t="n">
+      <c r="N55" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="O55" t="inlineStr">
@@ -3475,6 +3757,11 @@
       </c>
       <c r="Q55" t="b">
         <v>0</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -3514,10 +3801,10 @@
       <c r="L56" t="n">
         <v>2.4</v>
       </c>
-      <c r="M56" s="1" t="n">
+      <c r="M56" s="2" t="n">
         <v>46135.53359953704</v>
       </c>
-      <c r="N56" s="1" t="n">
+      <c r="N56" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="O56" t="inlineStr">
@@ -3530,6 +3817,11 @@
       </c>
       <c r="Q56" t="b">
         <v>0</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -3569,10 +3861,10 @@
       <c r="L57" t="n">
         <v>7</v>
       </c>
-      <c r="M57" s="1" t="n">
+      <c r="M57" s="2" t="n">
         <v>46135.68820601852</v>
       </c>
-      <c r="N57" s="1" t="n">
+      <c r="N57" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="O57" t="inlineStr">
@@ -3585,6 +3877,11 @@
       </c>
       <c r="Q57" t="b">
         <v>0</v>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -3624,10 +3921,10 @@
       <c r="L58" t="n">
         <v>7</v>
       </c>
-      <c r="M58" s="1" t="n">
+      <c r="M58" s="2" t="n">
         <v>46135.86390046297</v>
       </c>
-      <c r="N58" s="1" t="n">
+      <c r="N58" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="O58" t="inlineStr">
@@ -3640,6 +3937,11 @@
       </c>
       <c r="Q58" t="b">
         <v>0</v>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -3679,10 +3981,10 @@
       <c r="L59" t="n">
         <v>7</v>
       </c>
-      <c r="M59" s="1" t="n">
+      <c r="M59" s="2" t="n">
         <v>46136.02126157407</v>
       </c>
-      <c r="N59" s="1" t="n">
+      <c r="N59" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="O59" t="inlineStr">
@@ -3695,6 +3997,11 @@
       </c>
       <c r="Q59" t="b">
         <v>0</v>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -3734,10 +4041,10 @@
       <c r="L60" t="n">
         <v>6.9</v>
       </c>
-      <c r="M60" s="1" t="n">
+      <c r="M60" s="2" t="n">
         <v>46136.18943287037</v>
       </c>
-      <c r="N60" s="1" t="n">
+      <c r="N60" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="O60" t="inlineStr">
@@ -3750,6 +4057,11 @@
       </c>
       <c r="Q60" t="b">
         <v>0</v>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -3789,10 +4101,10 @@
       <c r="L61" t="n">
         <v>6.9</v>
       </c>
-      <c r="M61" s="1" t="n">
+      <c r="M61" s="2" t="n">
         <v>46136.35768518518</v>
       </c>
-      <c r="N61" s="1" t="n">
+      <c r="N61" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="O61" t="inlineStr">
@@ -3805,6 +4117,11 @@
       </c>
       <c r="Q61" t="b">
         <v>0</v>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -3844,10 +4161,10 @@
       <c r="L62" t="n">
         <v>7</v>
       </c>
-      <c r="M62" s="1" t="n">
+      <c r="M62" s="2" t="n">
         <v>46136.52224537037</v>
       </c>
-      <c r="N62" s="1" t="n">
+      <c r="N62" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="O62" t="inlineStr">
@@ -3860,6 +4177,11 @@
       </c>
       <c r="Q62" t="b">
         <v>1</v>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>⚠️ Anomaly</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -3899,10 +4221,10 @@
       <c r="L63" t="n">
         <v>2.6</v>
       </c>
-      <c r="M63" s="1" t="n">
+      <c r="M63" s="2" t="n">
         <v>46136.6883912037</v>
       </c>
-      <c r="N63" s="1" t="n">
+      <c r="N63" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="O63" t="inlineStr">
@@ -3915,6 +4237,11 @@
       </c>
       <c r="Q63" t="b">
         <v>0</v>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -3954,10 +4281,10 @@
       <c r="L64" t="n">
         <v>2.6</v>
       </c>
-      <c r="M64" s="1" t="n">
+      <c r="M64" s="2" t="n">
         <v>46136.85456018519</v>
       </c>
-      <c r="N64" s="1" t="n">
+      <c r="N64" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="O64" t="inlineStr">
@@ -3970,6 +4297,11 @@
       </c>
       <c r="Q64" t="b">
         <v>0</v>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -4009,10 +4341,10 @@
       <c r="L65" t="n">
         <v>2.6</v>
       </c>
-      <c r="M65" s="1" t="n">
+      <c r="M65" s="2" t="n">
         <v>46137.0588425926</v>
       </c>
-      <c r="N65" s="1" t="n">
+      <c r="N65" s="2" t="n">
         <v>46137</v>
       </c>
       <c r="O65" t="inlineStr">
@@ -4025,6 +4357,11 @@
       </c>
       <c r="Q65" t="b">
         <v>0</v>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -4064,10 +4401,10 @@
       <c r="L66" t="n">
         <v>7.2</v>
       </c>
-      <c r="M66" s="1" t="n">
+      <c r="M66" s="2" t="n">
         <v>46137.18950231482</v>
       </c>
-      <c r="N66" s="1" t="n">
+      <c r="N66" s="2" t="n">
         <v>46137</v>
       </c>
       <c r="O66" t="inlineStr">
@@ -4080,6 +4417,11 @@
       </c>
       <c r="Q66" t="b">
         <v>0</v>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -4119,10 +4461,10 @@
       <c r="L67" t="n">
         <v>7</v>
       </c>
-      <c r="M67" s="1" t="n">
+      <c r="M67" s="2" t="n">
         <v>46137.36697916667</v>
       </c>
-      <c r="N67" s="1" t="n">
+      <c r="N67" s="2" t="n">
         <v>46137</v>
       </c>
       <c r="O67" t="inlineStr">
@@ -4135,6 +4477,11 @@
       </c>
       <c r="Q67" t="b">
         <v>0</v>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -4174,10 +4521,10 @@
       <c r="L68" t="n">
         <v>7</v>
       </c>
-      <c r="M68" s="1" t="n">
+      <c r="M68" s="2" t="n">
         <v>46137.52636574074</v>
       </c>
-      <c r="N68" s="1" t="n">
+      <c r="N68" s="2" t="n">
         <v>46137</v>
       </c>
       <c r="O68" t="inlineStr">
@@ -4190,6 +4537,11 @@
       </c>
       <c r="Q68" t="b">
         <v>0</v>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -4229,10 +4581,10 @@
       <c r="L69" t="n">
         <v>6.9</v>
       </c>
-      <c r="M69" s="1" t="n">
+      <c r="M69" s="2" t="n">
         <v>46137.68905092592</v>
       </c>
-      <c r="N69" s="1" t="n">
+      <c r="N69" s="2" t="n">
         <v>46137</v>
       </c>
       <c r="O69" t="inlineStr">
@@ -4245,6 +4597,11 @@
       </c>
       <c r="Q69" t="b">
         <v>0</v>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -4284,10 +4641,10 @@
       <c r="L70" t="n">
         <v>6.9</v>
       </c>
-      <c r="M70" s="1" t="n">
+      <c r="M70" s="2" t="n">
         <v>46137.8555787037</v>
       </c>
-      <c r="N70" s="1" t="n">
+      <c r="N70" s="2" t="n">
         <v>46137</v>
       </c>
       <c r="O70" t="inlineStr">
@@ -4300,6 +4657,11 @@
       </c>
       <c r="Q70" t="b">
         <v>0</v>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -4339,10 +4701,10 @@
       <c r="L71" t="n">
         <v>6.9</v>
       </c>
-      <c r="M71" s="1" t="n">
+      <c r="M71" s="2" t="n">
         <v>46138.08900462963</v>
       </c>
-      <c r="N71" s="1" t="n">
+      <c r="N71" s="2" t="n">
         <v>46138</v>
       </c>
       <c r="O71" t="inlineStr">
@@ -4355,6 +4717,11 @@
       </c>
       <c r="Q71" t="b">
         <v>0</v>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -4394,10 +4761,10 @@
       <c r="L72" t="n">
         <v>6.9</v>
       </c>
-      <c r="M72" s="1" t="n">
+      <c r="M72" s="2" t="n">
         <v>46138.22342592593</v>
       </c>
-      <c r="N72" s="1" t="n">
+      <c r="N72" s="2" t="n">
         <v>46138</v>
       </c>
       <c r="O72" t="inlineStr">
@@ -4410,6 +4777,11 @@
       </c>
       <c r="Q72" t="b">
         <v>0</v>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -4449,10 +4821,10 @@
       <c r="L73" t="n">
         <v>6.9</v>
       </c>
-      <c r="M73" s="1" t="n">
+      <c r="M73" s="2" t="n">
         <v>46138.35784722222</v>
       </c>
-      <c r="N73" s="1" t="n">
+      <c r="N73" s="2" t="n">
         <v>46138</v>
       </c>
       <c r="O73" t="inlineStr">
@@ -4465,6 +4837,11 @@
       </c>
       <c r="Q73" t="b">
         <v>0</v>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -4504,10 +4881,10 @@
       <c r="L74" t="n">
         <v>6.9</v>
       </c>
-      <c r="M74" s="1" t="n">
+      <c r="M74" s="2" t="n">
         <v>46138.54626157408</v>
       </c>
-      <c r="N74" s="1" t="n">
+      <c r="N74" s="2" t="n">
         <v>46138</v>
       </c>
       <c r="O74" t="inlineStr">
@@ -4520,6 +4897,11 @@
       </c>
       <c r="Q74" t="b">
         <v>0</v>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -4559,10 +4941,10 @@
       <c r="L75" t="n">
         <v>7</v>
       </c>
-      <c r="M75" s="1" t="n">
+      <c r="M75" s="2" t="n">
         <v>46138.69407407408</v>
       </c>
-      <c r="N75" s="1" t="n">
+      <c r="N75" s="2" t="n">
         <v>46138</v>
       </c>
       <c r="O75" t="inlineStr">
@@ -4575,6 +4957,11 @@
       </c>
       <c r="Q75" t="b">
         <v>0</v>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -4614,10 +5001,10 @@
       <c r="L76" t="n">
         <v>7</v>
       </c>
-      <c r="M76" s="1" t="n">
+      <c r="M76" s="2" t="n">
         <v>46138.85946759259</v>
       </c>
-      <c r="N76" s="1" t="n">
+      <c r="N76" s="2" t="n">
         <v>46138</v>
       </c>
       <c r="O76" t="inlineStr">
@@ -4630,6 +5017,11 @@
       </c>
       <c r="Q76" t="b">
         <v>0</v>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -4669,10 +5061,10 @@
       <c r="L77" t="n">
         <v>7.1</v>
       </c>
-      <c r="M77" s="1" t="n">
+      <c r="M77" s="2" t="n">
         <v>46139.04685185185</v>
       </c>
-      <c r="N77" s="1" t="n">
+      <c r="N77" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="O77" t="inlineStr">
@@ -4685,6 +5077,11 @@
       </c>
       <c r="Q77" t="b">
         <v>0</v>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -4724,10 +5121,10 @@
       <c r="L78" t="n">
         <v>2.4</v>
       </c>
-      <c r="M78" s="1" t="n">
+      <c r="M78" s="2" t="n">
         <v>46139.20314814815</v>
       </c>
-      <c r="N78" s="1" t="n">
+      <c r="N78" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="O78" t="inlineStr">
@@ -4740,6 +5137,11 @@
       </c>
       <c r="Q78" t="b">
         <v>0</v>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -4779,10 +5181,10 @@
       <c r="L79" t="n">
         <v>2.4</v>
       </c>
-      <c r="M79" s="1" t="n">
+      <c r="M79" s="2" t="n">
         <v>46139.35634259259</v>
       </c>
-      <c r="N79" s="1" t="n">
+      <c r="N79" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="O79" t="inlineStr">
@@ -4795,6 +5197,11 @@
       </c>
       <c r="Q79" t="b">
         <v>0</v>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -4834,10 +5241,10 @@
       <c r="L80" t="n">
         <v>2.3</v>
       </c>
-      <c r="M80" s="1" t="n">
+      <c r="M80" s="2" t="n">
         <v>46139.52431712963</v>
       </c>
-      <c r="N80" s="1" t="n">
+      <c r="N80" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="O80" t="inlineStr">
@@ -4850,6 +5257,11 @@
       </c>
       <c r="Q80" t="b">
         <v>1</v>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>⚠️ Anomaly</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -4889,10 +5301,10 @@
       <c r="L81" t="n">
         <v>7.2</v>
       </c>
-      <c r="M81" s="1" t="n">
+      <c r="M81" s="2" t="n">
         <v>46139.69873842593</v>
       </c>
-      <c r="N81" s="1" t="n">
+      <c r="N81" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="O81" t="inlineStr">
@@ -4905,6 +5317,11 @@
       </c>
       <c r="Q81" t="b">
         <v>0</v>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -4944,10 +5361,10 @@
       <c r="L82" t="n">
         <v>7.3</v>
       </c>
-      <c r="M82" s="1" t="n">
+      <c r="M82" s="2" t="n">
         <v>46139.86931712963</v>
       </c>
-      <c r="N82" s="1" t="n">
+      <c r="N82" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="O82" t="inlineStr">
@@ -4960,6 +5377,11 @@
       </c>
       <c r="Q82" t="b">
         <v>1</v>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>⚠️ Anomaly</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -4999,10 +5421,10 @@
       <c r="L83" t="n">
         <v>7.6</v>
       </c>
-      <c r="M83" s="1" t="n">
+      <c r="M83" s="2" t="n">
         <v>46140.02158564814</v>
       </c>
-      <c r="N83" s="1" t="n">
+      <c r="N83" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="O83" t="inlineStr">
@@ -5015,6 +5437,11 @@
       </c>
       <c r="Q83" t="b">
         <v>0</v>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -5054,10 +5481,10 @@
       <c r="L84" t="n">
         <v>7.4</v>
       </c>
-      <c r="M84" s="1" t="n">
+      <c r="M84" s="2" t="n">
         <v>46140.19370370371</v>
       </c>
-      <c r="N84" s="1" t="n">
+      <c r="N84" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="O84" t="inlineStr">
@@ -5070,6 +5497,11 @@
       </c>
       <c r="Q84" t="b">
         <v>0</v>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -5109,10 +5541,10 @@
       <c r="L85" t="n">
         <v>7.1</v>
       </c>
-      <c r="M85" s="1" t="n">
+      <c r="M85" s="2" t="n">
         <v>46140.35989583333</v>
       </c>
-      <c r="N85" s="1" t="n">
+      <c r="N85" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="O85" t="inlineStr">
@@ -5125,6 +5557,11 @@
       </c>
       <c r="Q85" t="b">
         <v>0</v>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -5164,10 +5601,10 @@
       <c r="L86" t="n">
         <v>7.2</v>
       </c>
-      <c r="M86" s="1" t="n">
+      <c r="M86" s="2" t="n">
         <v>46140.52547453704</v>
       </c>
-      <c r="N86" s="1" t="n">
+      <c r="N86" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="O86" t="inlineStr">
@@ -5180,6 +5617,11 @@
       </c>
       <c r="Q86" t="b">
         <v>0</v>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -5219,10 +5661,10 @@
       <c r="L87" t="n">
         <v>2.5</v>
       </c>
-      <c r="M87" s="1" t="n">
+      <c r="M87" s="2" t="n">
         <v>46140.69204861111</v>
       </c>
-      <c r="N87" s="1" t="n">
+      <c r="N87" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="O87" t="inlineStr">
@@ -5235,6 +5677,11 @@
       </c>
       <c r="Q87" t="b">
         <v>0</v>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -5274,10 +5721,10 @@
       <c r="L88" t="n">
         <v>2.5</v>
       </c>
-      <c r="M88" s="1" t="n">
+      <c r="M88" s="2" t="n">
         <v>46140.85797453704</v>
       </c>
-      <c r="N88" s="1" t="n">
+      <c r="N88" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="O88" t="inlineStr">
@@ -5290,6 +5737,11 @@
       </c>
       <c r="Q88" t="b">
         <v>0</v>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -5329,10 +5781,10 @@
       <c r="L89" t="n">
         <v>2.5</v>
       </c>
-      <c r="M89" s="1" t="n">
+      <c r="M89" s="2" t="n">
         <v>46141.08907407407</v>
       </c>
-      <c r="N89" s="1" t="n">
+      <c r="N89" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="O89" t="inlineStr">
@@ -5345,6 +5797,11 @@
       </c>
       <c r="Q89" t="b">
         <v>1</v>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>⚠️ Anomaly</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -5384,10 +5841,10 @@
       <c r="L90" t="n">
         <v>7</v>
       </c>
-      <c r="M90" s="1" t="n">
+      <c r="M90" s="2" t="n">
         <v>46141.19405092593</v>
       </c>
-      <c r="N90" s="1" t="n">
+      <c r="N90" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="O90" t="inlineStr">
@@ -5400,6 +5857,11 @@
       </c>
       <c r="Q90" t="b">
         <v>0</v>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -5439,10 +5901,10 @@
       <c r="L91" t="n">
         <v>6.7</v>
       </c>
-      <c r="M91" s="1" t="n">
+      <c r="M91" s="2" t="n">
         <v>46141.37282407407</v>
       </c>
-      <c r="N91" s="1" t="n">
+      <c r="N91" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="O91" t="inlineStr">
@@ -5455,6 +5917,11 @@
       </c>
       <c r="Q91" t="b">
         <v>1</v>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>⚠️ Anomaly</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -5494,10 +5961,10 @@
       <c r="L92" t="n">
         <v>6.7</v>
       </c>
-      <c r="M92" s="1" t="n">
+      <c r="M92" s="2" t="n">
         <v>46141.52434027778</v>
       </c>
-      <c r="N92" s="1" t="n">
+      <c r="N92" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="O92" t="inlineStr">
@@ -5510,6 +5977,11 @@
       </c>
       <c r="Q92" t="b">
         <v>0</v>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -5549,10 +6021,10 @@
       <c r="L93" t="n">
         <v>7</v>
       </c>
-      <c r="M93" s="1" t="n">
+      <c r="M93" s="2" t="n">
         <v>46141.69369212963</v>
       </c>
-      <c r="N93" s="1" t="n">
+      <c r="N93" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="O93" t="inlineStr">
@@ -5565,6 +6037,11 @@
       </c>
       <c r="Q93" t="b">
         <v>0</v>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -5604,10 +6081,10 @@
       <c r="L94" t="n">
         <v>7.7</v>
       </c>
-      <c r="M94" s="1" t="n">
+      <c r="M94" s="2" t="n">
         <v>46141.85452546296</v>
       </c>
-      <c r="N94" s="1" t="n">
+      <c r="N94" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="O94" t="inlineStr">
@@ -5620,6 +6097,11 @@
       </c>
       <c r="Q94" t="b">
         <v>0</v>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -5659,10 +6141,10 @@
       <c r="L95" t="n">
         <v>7.7</v>
       </c>
-      <c r="M95" s="1" t="n">
+      <c r="M95" s="2" t="n">
         <v>46142.09556712963</v>
       </c>
-      <c r="N95" s="1" t="n">
+      <c r="N95" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="O95" t="inlineStr">
@@ -5675,6 +6157,11 @@
       </c>
       <c r="Q95" t="b">
         <v>0</v>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -5714,10 +6201,10 @@
       <c r="L96" t="n">
         <v>7.7</v>
       </c>
-      <c r="M96" s="1" t="n">
+      <c r="M96" s="2" t="n">
         <v>46142.22015046296</v>
       </c>
-      <c r="N96" s="1" t="n">
+      <c r="N96" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="O96" t="inlineStr">
@@ -5730,6 +6217,11 @@
       </c>
       <c r="Q96" t="b">
         <v>0</v>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +6261,10 @@
       <c r="L97" t="n">
         <v>7.4</v>
       </c>
-      <c r="M97" s="1" t="n">
+      <c r="M97" s="2" t="n">
         <v>46142.35427083333</v>
       </c>
-      <c r="N97" s="1" t="n">
+      <c r="N97" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="O97" t="inlineStr">
@@ -5785,6 +6277,11 @@
       </c>
       <c r="Q97" t="b">
         <v>0</v>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -5824,10 +6321,10 @@
       <c r="L98" t="n">
         <v>7.5</v>
       </c>
-      <c r="M98" s="1" t="n">
+      <c r="M98" s="2" t="n">
         <v>46142.52810185185</v>
       </c>
-      <c r="N98" s="1" t="n">
+      <c r="N98" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="O98" t="inlineStr">
@@ -5840,6 +6337,11 @@
       </c>
       <c r="Q98" t="b">
         <v>0</v>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -5879,10 +6381,10 @@
       <c r="L99" t="n">
         <v>7.9</v>
       </c>
-      <c r="M99" s="1" t="n">
+      <c r="M99" s="2" t="n">
         <v>46142.70089120371</v>
       </c>
-      <c r="N99" s="1" t="n">
+      <c r="N99" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="O99" t="inlineStr">
@@ -5895,6 +6397,11 @@
       </c>
       <c r="Q99" t="b">
         <v>0</v>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -5934,10 +6441,10 @@
       <c r="L100" t="n">
         <v>7.9</v>
       </c>
-      <c r="M100" s="1" t="n">
+      <c r="M100" s="2" t="n">
         <v>46142.85965277778</v>
       </c>
-      <c r="N100" s="1" t="n">
+      <c r="N100" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="O100" t="inlineStr">
@@ -5950,6 +6457,11 @@
       </c>
       <c r="Q100" t="b">
         <v>0</v>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -5989,10 +6501,10 @@
       <c r="L101" t="n">
         <v>7.9</v>
       </c>
-      <c r="M101" s="1" t="n">
+      <c r="M101" s="2" t="n">
         <v>46143.02594907407</v>
       </c>
-      <c r="N101" s="1" t="n">
+      <c r="N101" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="O101" t="inlineStr">
@@ -6005,6 +6517,11 @@
       </c>
       <c r="Q101" t="b">
         <v>0</v>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -6044,10 +6561,10 @@
       <c r="L102" t="n">
         <v>2.5</v>
       </c>
-      <c r="M102" s="1" t="n">
+      <c r="M102" s="2" t="n">
         <v>46143.20488425926</v>
       </c>
-      <c r="N102" s="1" t="n">
+      <c r="N102" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="O102" t="inlineStr">
@@ -6060,6 +6577,11 @@
       </c>
       <c r="Q102" t="b">
         <v>1</v>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>⚠️ Anomaly</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -6099,10 +6621,10 @@
       <c r="L103" t="n">
         <v>2.5</v>
       </c>
-      <c r="M103" s="1" t="n">
+      <c r="M103" s="2" t="n">
         <v>46143.35506944444</v>
       </c>
-      <c r="N103" s="1" t="n">
+      <c r="N103" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="O103" t="inlineStr">
@@ -6115,6 +6637,11 @@
       </c>
       <c r="Q103" t="b">
         <v>0</v>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -6154,10 +6681,10 @@
       <c r="L104" t="n">
         <v>2.5</v>
       </c>
-      <c r="M104" s="1" t="n">
+      <c r="M104" s="2" t="n">
         <v>46143.52101851852</v>
       </c>
-      <c r="N104" s="1" t="n">
+      <c r="N104" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="O104" t="inlineStr">
@@ -6170,6 +6697,11 @@
       </c>
       <c r="Q104" t="b">
         <v>0</v>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="105">
@@ -6209,10 +6741,10 @@
       <c r="L105" t="n">
         <v>7.9</v>
       </c>
-      <c r="M105" s="1" t="n">
+      <c r="M105" s="2" t="n">
         <v>46143.69318287037</v>
       </c>
-      <c r="N105" s="1" t="n">
+      <c r="N105" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="O105" t="inlineStr">
@@ -6225,6 +6757,11 @@
       </c>
       <c r="Q105" t="b">
         <v>0</v>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -6264,10 +6801,10 @@
       <c r="L106" t="n">
         <v>7.9</v>
       </c>
-      <c r="M106" s="1" t="n">
+      <c r="M106" s="2" t="n">
         <v>46143.86835648148</v>
       </c>
-      <c r="N106" s="1" t="n">
+      <c r="N106" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="O106" t="inlineStr">
@@ -6280,6 +6817,11 @@
       </c>
       <c r="Q106" t="b">
         <v>0</v>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -6319,10 +6861,10 @@
       <c r="L107" t="n">
         <v>7.9</v>
       </c>
-      <c r="M107" s="1" t="n">
+      <c r="M107" s="2" t="n">
         <v>46144.02177083334</v>
       </c>
-      <c r="N107" s="1" t="n">
+      <c r="N107" s="2" t="n">
         <v>46144</v>
       </c>
       <c r="O107" t="inlineStr">
@@ -6335,6 +6877,11 @@
       </c>
       <c r="Q107" t="b">
         <v>0</v>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="108">
@@ -6374,10 +6921,10 @@
       <c r="L108" t="n">
         <v>7.7</v>
       </c>
-      <c r="M108" s="1" t="n">
+      <c r="M108" s="2" t="n">
         <v>46144.18803240741</v>
       </c>
-      <c r="N108" s="1" t="n">
+      <c r="N108" s="2" t="n">
         <v>46144</v>
       </c>
       <c r="O108" t="inlineStr">
@@ -6390,6 +6937,11 @@
       </c>
       <c r="Q108" t="b">
         <v>0</v>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -6429,10 +6981,10 @@
       <c r="L109" t="n">
         <v>7.4</v>
       </c>
-      <c r="M109" s="1" t="n">
+      <c r="M109" s="2" t="n">
         <v>46144.35827546296</v>
       </c>
-      <c r="N109" s="1" t="n">
+      <c r="N109" s="2" t="n">
         <v>46144</v>
       </c>
       <c r="O109" t="inlineStr">
@@ -6445,6 +6997,11 @@
       </c>
       <c r="Q109" t="b">
         <v>0</v>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -6484,10 +7041,10 @@
       <c r="L110" t="n">
         <v>7.6</v>
       </c>
-      <c r="M110" s="1" t="n">
+      <c r="M110" s="2" t="n">
         <v>46144.52101851852</v>
       </c>
-      <c r="N110" s="1" t="n">
+      <c r="N110" s="2" t="n">
         <v>46144</v>
       </c>
       <c r="O110" t="inlineStr">
@@ -6500,6 +7057,11 @@
       </c>
       <c r="Q110" t="b">
         <v>1</v>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>⚠️ Anomaly</t>
+        </is>
       </c>
     </row>
     <row r="111">
@@ -6539,10 +7101,10 @@
       <c r="L111" t="n">
         <v>2.5</v>
       </c>
-      <c r="M111" s="1" t="n">
+      <c r="M111" s="2" t="n">
         <v>46144.69450231481</v>
       </c>
-      <c r="N111" s="1" t="n">
+      <c r="N111" s="2" t="n">
         <v>46144</v>
       </c>
       <c r="O111" t="inlineStr">
@@ -6555,6 +7117,11 @@
       </c>
       <c r="Q111" t="b">
         <v>0</v>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -6594,10 +7161,10 @@
       <c r="L112" t="n">
         <v>2.5</v>
       </c>
-      <c r="M112" s="1" t="n">
+      <c r="M112" s="2" t="n">
         <v>46144.85748842593</v>
       </c>
-      <c r="N112" s="1" t="n">
+      <c r="N112" s="2" t="n">
         <v>46144</v>
       </c>
       <c r="O112" t="inlineStr">
@@ -6610,6 +7177,11 @@
       </c>
       <c r="Q112" t="b">
         <v>0</v>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -6649,10 +7221,10 @@
       <c r="L113" t="n">
         <v>2.4</v>
       </c>
-      <c r="M113" s="1" t="n">
+      <c r="M113" s="2" t="n">
         <v>46145.06841435185</v>
       </c>
-      <c r="N113" s="1" t="n">
+      <c r="N113" s="2" t="n">
         <v>46145</v>
       </c>
       <c r="O113" t="inlineStr">
@@ -6665,6 +7237,11 @@
       </c>
       <c r="Q113" t="b">
         <v>0</v>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -6704,10 +7281,10 @@
       <c r="L114" t="n">
         <v>7.8</v>
       </c>
-      <c r="M114" s="1" t="n">
+      <c r="M114" s="2" t="n">
         <v>46145.20671296296</v>
       </c>
-      <c r="N114" s="1" t="n">
+      <c r="N114" s="2" t="n">
         <v>46145</v>
       </c>
       <c r="O114" t="inlineStr">
@@ -6720,6 +7297,11 @@
       </c>
       <c r="Q114" t="b">
         <v>0</v>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="115">
@@ -6759,10 +7341,10 @@
       <c r="L115" t="n">
         <v>7.2</v>
       </c>
-      <c r="M115" s="1" t="n">
+      <c r="M115" s="2" t="n">
         <v>46145.35491898148</v>
       </c>
-      <c r="N115" s="1" t="n">
+      <c r="N115" s="2" t="n">
         <v>46145</v>
       </c>
       <c r="O115" t="inlineStr">
@@ -6775,6 +7357,11 @@
       </c>
       <c r="Q115" t="b">
         <v>0</v>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -6814,10 +7401,10 @@
       <c r="L116" t="n">
         <v>7.2</v>
       </c>
-      <c r="M116" s="1" t="n">
+      <c r="M116" s="2" t="n">
         <v>46145.52814814815</v>
       </c>
-      <c r="N116" s="1" t="n">
+      <c r="N116" s="2" t="n">
         <v>46145</v>
       </c>
       <c r="O116" t="inlineStr">
@@ -6830,6 +7417,11 @@
       </c>
       <c r="Q116" t="b">
         <v>1</v>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>⚠️ Anomaly</t>
+        </is>
       </c>
     </row>
     <row r="117">
@@ -6869,10 +7461,10 @@
       <c r="L117" t="n">
         <v>7.6</v>
       </c>
-      <c r="M117" s="1" t="n">
+      <c r="M117" s="2" t="n">
         <v>46145.69175925926</v>
       </c>
-      <c r="N117" s="1" t="n">
+      <c r="N117" s="2" t="n">
         <v>46145</v>
       </c>
       <c r="O117" t="inlineStr">
@@ -6885,6 +7477,11 @@
       </c>
       <c r="Q117" t="b">
         <v>0</v>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -6924,10 +7521,10 @@
       <c r="L118" t="n">
         <v>7.5</v>
       </c>
-      <c r="M118" s="1" t="n">
+      <c r="M118" s="2" t="n">
         <v>46145.85527777778</v>
       </c>
-      <c r="N118" s="1" t="n">
+      <c r="N118" s="2" t="n">
         <v>46145</v>
       </c>
       <c r="O118" t="inlineStr">
@@ -6940,6 +7537,11 @@
       </c>
       <c r="Q118" t="b">
         <v>0</v>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -6979,10 +7581,10 @@
       <c r="L119" t="n">
         <v>7.5</v>
       </c>
-      <c r="M119" s="1" t="n">
+      <c r="M119" s="2" t="n">
         <v>46146.09436342592</v>
       </c>
-      <c r="N119" s="1" t="n">
+      <c r="N119" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="O119" t="inlineStr">
@@ -6995,6 +7597,11 @@
       </c>
       <c r="Q119" t="b">
         <v>0</v>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -7034,10 +7641,10 @@
       <c r="L120" t="n">
         <v>7.5</v>
       </c>
-      <c r="M120" s="1" t="n">
+      <c r="M120" s="2" t="n">
         <v>46146.21984953704</v>
       </c>
-      <c r="N120" s="1" t="n">
+      <c r="N120" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="O120" t="inlineStr">
@@ -7050,6 +7657,11 @@
       </c>
       <c r="Q120" t="b">
         <v>0</v>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
   </sheetData>
